--- a/artfynd/A 1177-2024 artfynd.xlsx
+++ b/artfynd/A 1177-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115955483</v>
+        <v>115955436</v>
       </c>
       <c r="B2" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,14 +722,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sandfallet NNO 660 m, Ög</t>
+          <t>Sandfallet NNO 650 m, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>531000</v>
+        <v>530989</v>
       </c>
       <c r="R2" t="n">
-        <v>6513496</v>
+        <v>6513490</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -767,11 +762,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-04-13</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ca 35 skott</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,15 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115955436</v>
+        <v>115955483</v>
       </c>
       <c r="B3" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -839,7 +824,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -856,14 +841,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sandfallet NNO 650 m, Ög</t>
+          <t>Sandfallet NNO 660 m, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530989</v>
+        <v>531000</v>
       </c>
       <c r="R3" t="n">
-        <v>6513490</v>
+        <v>6513496</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,6 +881,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-04-13</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ca 35 skott</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 1177-2024 artfynd.xlsx
+++ b/artfynd/A 1177-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115955436</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -915,8 +925,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115955483</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>